--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAIXA DIREÇÃO - 30_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAIXA DIREÇÃO - 30_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,7 +448,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -508,11 +500,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +520,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +540,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +560,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +580,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +600,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +620,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -659,7 +640,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -680,7 +660,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -701,7 +680,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -722,7 +700,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -743,7 +720,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -764,7 +740,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -785,7 +760,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -806,7 +780,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -827,7 +800,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -848,7 +820,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -869,7 +840,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -890,7 +860,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -911,7 +880,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -932,11 +900,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -957,7 +920,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -978,7 +940,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -995,11 +956,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1016,7 +972,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1031,11 +986,6 @@
       <c r="D30" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>105</t>
         </is>
       </c>
     </row>
